--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487651_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487651_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5012</v>
+        <v>7.9288</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6622</v>
+        <v>6.0626</v>
       </c>
       <c r="F2" t="n">
-        <v>1.839</v>
+        <v>1.8662</v>
       </c>
       <c r="G2" t="n">
         <v>6.326</v>
@@ -610,13 +610,13 @@
         <v>2.7164</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0188</v>
+        <v>0.4088</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4834</v>
+        <v>-0.083</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4646</v>
+        <v>0.4919</v>
       </c>
       <c r="V2" t="n">
         <v>0.6119</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5791</v>
+        <v>6.2436</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2253</v>
+        <v>0.6257</v>
       </c>
       <c r="F3" t="n">
-        <v>6.3538</v>
+        <v>5.6179</v>
       </c>
       <c r="G3" t="n">
         <v>4.0787</v>
@@ -688,13 +688,13 @@
         <v>1.7463</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6169</v>
+        <v>1.2814</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4229</v>
+        <v>-0.0225</v>
       </c>
       <c r="U3" t="n">
-        <v>2.0398</v>
+        <v>1.3039</v>
       </c>
       <c r="V3" t="n">
         <v>1.2716</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3262</v>
+        <v>2.2167</v>
       </c>
       <c r="E4" t="n">
-        <v>0.19</v>
+        <v>-0.1103</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1362</v>
+        <v>2.3269</v>
       </c>
       <c r="G4" t="n">
         <v>1.4706</v>
@@ -766,13 +766,13 @@
         <v>1.7463</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3212</v>
+        <v>0.2117</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1222</v>
+        <v>-0.1781</v>
       </c>
       <c r="U4" t="n">
-        <v>0.199</v>
+        <v>0.3898</v>
       </c>
       <c r="V4" t="n">
         <v>-0.0478</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0717</v>
+        <v>1.2625</v>
       </c>
       <c r="E5" t="n">
         <v>0.1475</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9242</v>
+        <v>1.115</v>
       </c>
       <c r="G5" t="n">
         <v>2.0074</v>
@@ -844,13 +844,13 @@
         <v>1.3582</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.188</v>
+        <v>0.0028</v>
       </c>
       <c r="T5" t="n">
         <v>-0.12</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0679</v>
+        <v>0.1228</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9418</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. MANGUE NVOMO</t>
+          <t>J. MENDOZA ALVAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.414</v>
+        <v>0.2265</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6311</v>
+        <v>-1.5103</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2171</v>
+        <v>1.7367</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5009</v>
+        <v>1.1285</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1822</v>
+        <v>0.276</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3187</v>
+        <v>0.8525</v>
       </c>
       <c r="J6" t="n">
-        <v>1.93</v>
+        <v>0.6118</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3388</v>
+        <v>0.0206</v>
       </c>
       <c r="L6" t="n">
         <v>0.5911999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.429</v>
+        <v>0.5168</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1565</v>
+        <v>0.2554</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2725</v>
+        <v>0.2614</v>
       </c>
       <c r="P6" t="n">
         <v>-1.5523</v>
@@ -922,28 +922,28 @@
         <v>0.3881</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7952</v>
+        <v>-0.0095</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9713000000000001</v>
+        <v>-0.1817</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1761</v>
+        <v>0.1722</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3299</v>
+        <v>0.6597</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MENDOZA ALVAREZ</t>
+          <t>M. MANGUE NVOMO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1447</v>
+        <v>0.0498</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5103</v>
+        <v>0.1306</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6549</v>
+        <v>-0.0808</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1285</v>
+        <v>1.5009</v>
       </c>
       <c r="H7" t="n">
-        <v>0.276</v>
+        <v>1.1822</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8525</v>
+        <v>0.3187</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6118</v>
+        <v>1.93</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0206</v>
+        <v>1.3388</v>
       </c>
       <c r="L7" t="n">
         <v>0.5911999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5168</v>
+        <v>-0.429</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2554</v>
+        <v>-0.1565</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2614</v>
+        <v>-0.2725</v>
       </c>
       <c r="P7" t="n">
         <v>-1.5523</v>
@@ -1000,28 +1000,28 @@
         <v>0.3881</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.431</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1817</v>
+        <v>0.4708</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09039999999999999</v>
+        <v>-0.0398</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6597</v>
+        <v>-0.3299</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>J. PRATS PEINADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2362</v>
+        <v>-0.8638</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.3082</v>
+        <v>-0.1005</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0721</v>
+        <v>-0.7633</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1428</v>
+        <v>-0.7304</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2012</v>
+        <v>-0.0519</v>
       </c>
       <c r="I8" t="n">
-        <v>2.344</v>
+        <v>-0.6785</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3669</v>
+        <v>0.0206</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1204</v>
+        <v>0.0206</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7536</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.5097</v>
+        <v>-0.751</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0808</v>
+        <v>-0.0725</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5904</v>
+        <v>-0.6785</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.1344</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.0747</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9403</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6972</v>
+        <v>-0.1335</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8512</v>
+        <v>-0.1211</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8459</v>
+        <v>-0.0123</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9418</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PRATS PEINADO</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7548</v>
+        <v>-0.9458</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1005</v>
+        <v>-3.9088</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6543</v>
+        <v>2.9631</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7304</v>
+        <v>1.1428</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0519</v>
+        <v>-1.2012</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6785</v>
+        <v>2.344</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0206</v>
+        <v>-0.3669</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0206</v>
+        <v>-1.1204</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.7536</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.751</v>
+        <v>1.5097</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0725</v>
+        <v>-0.0808</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6785</v>
+        <v>1.5904</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-4.0747</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.9403</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0244</v>
+        <v>0.9876</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1211</v>
+        <v>0.2506</v>
       </c>
       <c r="U9" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.7369</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.9418</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0144</v>
+        <v>-1.8777</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7265</v>
+        <v>-4.4262</v>
       </c>
       <c r="F10" t="n">
-        <v>2.712</v>
+        <v>2.5485</v>
       </c>
       <c r="G10" t="n">
         <v>-2.494</v>
@@ -1234,13 +1234,13 @@
         <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9453</v>
+        <v>1.082</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0595</v>
+        <v>0.2408</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0047</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6597</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7891</v>
+        <v>-2.4254</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7177</v>
+        <v>-3.5175</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9286</v>
+        <v>1.0921</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3151</v>
@@ -1312,13 +1312,13 @@
         <v>0.9702</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5336</v>
+        <v>-0.1699</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2423</v>
+        <v>-0.0421</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2914</v>
+        <v>-0.1278</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3356</v>
+        <v>-3.9084</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5033</v>
+        <v>-2.4032</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8323</v>
+        <v>-1.5053</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8727</v>
@@ -1390,13 +1390,13 @@
         <v>1.1642</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5211</v>
+        <v>-0.0939</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2412</v>
+        <v>-0.1411</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2799</v>
+        <v>0.0471</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1657</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.9068</v>
+        <v>7.906799999999997</v>
       </c>
       <c r="E13" t="n">
         <v>-9.010399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>16.9171</v>
+        <v>16.917</v>
       </c>
       <c r="G13" t="n">
         <v>13.2427</v>
@@ -1468,13 +1468,13 @@
         <v>13.5823</v>
       </c>
       <c r="S13" t="n">
-        <v>3.9986</v>
+        <v>3.998499999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.07260000000000008</v>
+        <v>0.07259999999999991</v>
       </c>
       <c r="U13" t="n">
-        <v>3.925799999999999</v>
+        <v>3.9259</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5435</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8011</v>
+        <v>2.2005</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0796</v>
+        <v>-0.521</v>
       </c>
       <c r="F14" t="n">
         <v>2.7216</v>
@@ -1546,10 +1546,10 @@
         <v>1.1642</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3347</v>
+        <v>0.7341</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0318</v>
+        <v>0.4312</v>
       </c>
       <c r="U14" t="n">
         <v>0.3028</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. BAILLO HERNÁNDEZ</t>
+          <t>I. GARCIA GALLARDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7948</v>
+        <v>2.0394</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3749</v>
+        <v>0.8378</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4198</v>
+        <v>1.2016</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0494</v>
+        <v>0.6256</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0059</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9565</v>
+        <v>0.6907</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3306</v>
+        <v>1.2458</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3306</v>
+        <v>1.0834</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.1624</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2812</v>
+        <v>-0.6202</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3246</v>
+        <v>-1.1485</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9565</v>
+        <v>0.5283</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.194</v>
+        <v>3.2985</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7761</v>
+        <v>3.2985</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0558</v>
+        <v>-0.3788</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7907</v>
+        <v>-0.408</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2652</v>
+        <v>0.0292</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8836</v>
+        <v>-1.506</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6597</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. GARCIA GALLARDO</t>
+          <t>P. BARCALA BELTRAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4844</v>
+        <v>1.9335</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3373</v>
+        <v>0.0893</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1471</v>
+        <v>1.8442</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6256</v>
+        <v>2.4932</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.06510000000000001</v>
+        <v>2.2558</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6907</v>
+        <v>0.2375</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2458</v>
+        <v>2.8461</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0834</v>
+        <v>2.8589</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1624</v>
+        <v>-0.0127</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6202</v>
+        <v>-0.3529</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1485</v>
+        <v>-0.6031</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5283</v>
+        <v>0.2502</v>
       </c>
       <c r="P16" t="n">
-        <v>3.2985</v>
+        <v>0.3881</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R16" t="n">
         <v>3.2985</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9338</v>
+        <v>-0.618</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9085</v>
+        <v>-0.4105</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0253</v>
+        <v>-0.2075</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.506</v>
+        <v>-0.3299</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.506</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. BUHORSKYI</t>
+          <t>B. BAILLO HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0759</v>
+        <v>1.5757</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4051</v>
+        <v>1.3739</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6708</v>
+        <v>0.2018</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3378</v>
+        <v>0.0494</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2043</v>
+        <v>1.0059</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1335</v>
+        <v>-0.9565</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7003</v>
+        <v>1.3306</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7003</v>
+        <v>1.3306</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3625</v>
+        <v>-1.2812</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.496</v>
+        <v>-0.3246</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1335</v>
+        <v>-0.9565</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1642</v>
+        <v>-0.194</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5157</v>
+        <v>-0.1632</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3645</v>
+        <v>-0.2103</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1512</v>
+        <v>0.0471</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9418</v>
+        <v>1.8836</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6597</v>
+        <v>1.2239</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2821</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. BARCALA BELTRAN</t>
+          <t>D. BUHORSKYI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6966</v>
+        <v>0.6482</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7115</v>
+        <v>0.0047</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4081</v>
+        <v>0.6435</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4932</v>
+        <v>0.3378</v>
       </c>
       <c r="H18" t="n">
-        <v>2.2558</v>
+        <v>0.2043</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2375</v>
+        <v>0.1335</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8461</v>
+        <v>0.7003</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8589</v>
+        <v>0.7003</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0127</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3529</v>
+        <v>-0.3625</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6031</v>
+        <v>-0.496</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2502</v>
+        <v>0.1335</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.2985</v>
+        <v>1.1642</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8549</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2113</v>
+        <v>-0.0359</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6435</v>
+        <v>0.1239</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3299</v>
+        <v>-0.9418</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5642</v>
+        <v>-0.6597</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.894</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1163</v>
+        <v>0.1891</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6999</v>
+        <v>-0.5998</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8162</v>
+        <v>0.7889</v>
       </c>
       <c r="G19" t="n">
         <v>0.2954</v>
@@ -1936,13 +1936,13 @@
         <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>0.103</v>
+        <v>0.1758</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1817</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2847</v>
+        <v>0.2574</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2821</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9372</v>
+        <v>-1.7375</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3827</v>
+        <v>-2.4828</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4455</v>
+        <v>0.7453</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7903</v>
@@ -2014,13 +2014,13 @@
         <v>1.5523</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4365</v>
+        <v>-1.2368</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6046</v>
+        <v>-0.7047</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.832</v>
+        <v>-0.5322</v>
       </c>
       <c r="V20" t="n">
         <v>0.7075</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.193</v>
+        <v>-2.02</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5757</v>
+        <v>-1.3755</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6173</v>
+        <v>-0.6445</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0413</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1516</v>
+        <v>0.0213</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3028</v>
+        <v>-0.1026</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1512</v>
+        <v>0.1239</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3176</v>
+        <v>-2.3434</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2716</v>
+        <v>-2.3707</v>
       </c>
       <c r="F22" t="n">
-        <v>0.954</v>
+        <v>0.0273</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8817</v>
@@ -2170,13 +2170,13 @@
         <v>3.1045</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5717</v>
+        <v>-0.5975</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.817</v>
+        <v>-0.9161</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2452</v>
+        <v>0.3186</v>
       </c>
       <c r="V22" t="n">
         <v>0.9418</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. VILLANUEVA LAZARO</t>
+          <t>L. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1039</v>
+        <v>-4.6783</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5437</v>
+        <v>-5.5285</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4398</v>
+        <v>0.8502</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.3342</v>
+        <v>-7.5795</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1854</v>
+        <v>-5.9607</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.5195</v>
+        <v>-1.6188</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.0231</v>
+        <v>-6.2028</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2729</v>
+        <v>-4.8731</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.2961</v>
+        <v>-1.3296</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.311</v>
+        <v>-1.3767</v>
       </c>
       <c r="N23" t="n">
         <v>-1.0875</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2235</v>
+        <v>-0.2892</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5821</v>
+        <v>2.7164</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3284</v>
+        <v>2.7164</v>
       </c>
       <c r="S23" t="n">
-        <v>0.19</v>
+        <v>-1.6033</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4273</v>
+        <v>-1.1138</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2373</v>
+        <v>-0.4895</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3776</v>
+        <v>1.788</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.0373</v>
+        <v>1.788</v>
       </c>
       <c r="X23" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ SANCHEZ</t>
+          <t>P. VILLANUEVA LAZARO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.324</v>
+        <v>-5.7139</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.9289</v>
+        <v>-6.3445</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6049</v>
+        <v>0.6306</v>
       </c>
       <c r="G24" t="n">
-        <v>-7.5795</v>
+        <v>-4.3342</v>
       </c>
       <c r="H24" t="n">
-        <v>-5.9607</v>
+        <v>0.1854</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.6188</v>
+        <v>-4.5195</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.2028</v>
+        <v>-2.0231</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.8731</v>
+        <v>1.2729</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3296</v>
+        <v>-3.2961</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3767</v>
+        <v>-2.311</v>
       </c>
       <c r="N24" t="n">
         <v>-1.0875</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2892</v>
+        <v>-1.2235</v>
       </c>
       <c r="P24" t="n">
-        <v>2.7164</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R24" t="n">
-        <v>2.7164</v>
+        <v>2.3284</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.249</v>
+        <v>-0.4201</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.5142</v>
+        <v>-0.3735</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7348</v>
+        <v>-0.0465</v>
       </c>
       <c r="V24" t="n">
-        <v>1.788</v>
+        <v>-0.3776</v>
       </c>
       <c r="W24" t="n">
-        <v>1.788</v>
+        <v>-1.0373</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="25">
@@ -2359,7 +2359,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.906600000000001</v>
+        <v>-7.9067</v>
       </c>
       <c r="E25" t="n">
         <v>-16.9171</v>
@@ -2377,7 +2377,7 @@
         <v>-6.701000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.7359</v>
+        <v>-3.735899999999998</v>
       </c>
       <c r="K25" t="n">
         <v>0.8243</v>
@@ -2386,7 +2386,7 @@
         <v>-4.5598</v>
       </c>
       <c r="M25" t="n">
-        <v>-9.506799999999998</v>
+        <v>-9.5068</v>
       </c>
       <c r="N25" t="n">
         <v>-7.365500000000001</v>
@@ -2404,13 +2404,13 @@
         <v>20.3733</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.9983</v>
+        <v>-3.9985</v>
       </c>
       <c r="T25" t="n">
         <v>-3.9258</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.07259999999999966</v>
+        <v>-0.07279999999999993</v>
       </c>
       <c r="V25" t="n">
         <v>2.5432</v>
